--- a/data/templates/financial_template_v2_2026.xlsx
+++ b/data/templates/financial_template_v2_2026.xlsx
@@ -2939,20 +2939,20 @@
       <x:c r="BL16" s="63" t="s">
         <x:v>84</x:v>
       </x:c>
-      <x:c r="BM16" s="52" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="BN16" s="52" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="BO16" s="64" t="s">
-        <x:v>87</x:v>
+      <x:c r="BM16" s="52" t="str">
+        <x:v>Forecast Nov (25)</x:v>
+      </x:c>
+      <x:c r="BN16" s="52" t="str">
+        <x:v>Accrual Nov (25)</x:v>
+      </x:c>
+      <x:c r="BO16" s="64" t="str">
+        <x:v>Actual Nov (25)</x:v>
       </x:c>
       <x:c r="BP16" s="65" t="s">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="BQ16" s="63" t="s">
-        <x:v>88</x:v>
+      <x:c r="BQ16" s="63" t="str">
+        <x:v>Accrual Reversal Nov (25)</x:v>
       </x:c>
       <x:c r="BR16" s="52" t="s">
         <x:v>89</x:v>
